--- a/data/trans_dic/P15-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P15-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria</t>
+          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,29; 7,13</t>
+          <t>4,2; 6,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,39; 9,98</t>
+          <t>6,36; 9,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,71; 7,98</t>
+          <t>4,34; 7,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,23; 9,24</t>
+          <t>5,24; 9,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,74; 7,33</t>
+          <t>4,92; 7,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,97; 10,02</t>
+          <t>7,07; 10,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,72; 9,54</t>
+          <t>5,89; 9,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,88; 12,4</t>
+          <t>9,09; 12,15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,87; 6,79</t>
+          <t>4,92; 6,87</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,11; 9,4</t>
+          <t>7,14; 9,46</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,63; 8,1</t>
+          <t>5,69; 8,22</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,87; 10,37</t>
+          <t>8,01; 10,41</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,21; 9,95</t>
+          <t>7,21; 10,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,12; 10,99</t>
+          <t>8,04; 10,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,9; 6,96</t>
+          <t>4,9; 6,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,9; 7,04</t>
+          <t>3,91; 7,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,64; 5,8</t>
+          <t>3,53; 5,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,45; 7,81</t>
+          <t>5,5; 7,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,44; 5,27</t>
+          <t>3,47; 5,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,22; 5,55</t>
+          <t>3,33; 5,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,8; 7,58</t>
+          <t>5,86; 7,63</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,19; 8,95</t>
+          <t>7,1; 9,03</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,38; 5,82</t>
+          <t>4,46; 5,82</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,16; 6,01</t>
+          <t>3,97; 6,08</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,34; 10,16</t>
+          <t>5,33; 10,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,74; 7,79</t>
+          <t>3,66; 8,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,84; 8,08</t>
+          <t>3,74; 7,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,49; 7,57</t>
+          <t>3,48; 7,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,08; 7,17</t>
+          <t>3,2; 6,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,09; 9,29</t>
+          <t>4,15; 9,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,86; 7,8</t>
+          <t>3,75; 8,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,43; 6,1</t>
+          <t>3,58; 6,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,91; 7,98</t>
+          <t>4,86; 7,9</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,51; 7,78</t>
+          <t>4,43; 7,71</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,33; 7,25</t>
+          <t>4,27; 7,21</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,86; 6,24</t>
+          <t>3,84; 6,6</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,51; 8,33</t>
+          <t>6,48; 8,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,48; 9,38</t>
+          <t>7,53; 9,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,07; 6,77</t>
+          <t>5,08; 6,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,51; 6,8</t>
+          <t>4,48; 6,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,47; 6,11</t>
+          <t>4,5; 6,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,4; 8,11</t>
+          <t>6,41; 8,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,65; 6,38</t>
+          <t>4,62; 6,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,76; 6,71</t>
+          <t>4,71; 6,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,69; 6,93</t>
+          <t>5,74; 7,01</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,19; 8,48</t>
+          <t>7,2; 8,54</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,11; 6,26</t>
+          <t>5,08; 6,24</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,04; 6,48</t>
+          <t>5,05; 6,56</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria</t>
+          <t>Población que ha tenido un accidente en el último año que le ha causado heridas o lesiones suficientes para limitar su actividad normal y/o para necesitar asistencia sanitaria (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>44246; 73525</t>
+          <t>43361; 71979</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>62314; 97233</t>
+          <t>61939; 95860</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35519; 60203</t>
+          <t>32769; 58300</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26924; 47577</t>
+          <t>26981; 48251</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>62275; 96441</t>
+          <t>64713; 98925</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>93283; 134098</t>
+          <t>94564; 135045</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>56915; 94899</t>
+          <t>58576; 94646</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>67066; 93662</t>
+          <t>68711; 91824</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>114353; 159281</t>
+          <t>115552; 161307</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>164501; 217435</t>
+          <t>165127; 218708</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>98435; 141593</t>
+          <t>99503; 143804</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>99938; 131727</t>
+          <t>101759; 132273</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>122093; 168577</t>
+          <t>122076; 169265</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>159502; 215843</t>
+          <t>157846; 211690</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>101789; 144417</t>
+          <t>101819; 144095</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>89279; 161290</t>
+          <t>89655; 161968</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>57781; 92048</t>
+          <t>56050; 90909</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>95845; 137272</t>
+          <t>96659; 139530</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>68335; 104860</t>
+          <t>69051; 105455</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>71960; 124239</t>
+          <t>74458; 126286</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>190405; 248786</t>
+          <t>192117; 250188</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>267418; 333199</t>
+          <t>264125; 336039</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>177975; 236559</t>
+          <t>181209; 236608</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>188556; 272139</t>
+          <t>179662; 275357</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>29428; 56027</t>
+          <t>29402; 56100</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>17974; 37462</t>
+          <t>17620; 38947</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21023; 44211</t>
+          <t>20442; 42922</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22548; 48930</t>
+          <t>22520; 49295</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14696; 34153</t>
+          <t>15237; 33224</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18746; 42585</t>
+          <t>19044; 42412</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21199; 42838</t>
+          <t>20618; 44127</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>22670; 40291</t>
+          <t>23612; 40625</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>50474; 81982</t>
+          <t>49962; 81194</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>42423; 73152</t>
+          <t>41647; 72458</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>47486; 79438</t>
+          <t>46850; 79024</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>50461; 81609</t>
+          <t>50233; 86321</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>213412; 272920</t>
+          <t>212290; 275280</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>255706; 320934</t>
+          <t>257533; 321909</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>171078; 228763</t>
+          <t>171679; 225857</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>155673; 234796</t>
+          <t>154496; 233781</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>151081; 206321</t>
+          <t>151993; 204526</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>227345; 288260</t>
+          <t>227761; 293375</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>164248; 225432</t>
+          <t>163040; 221032</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>173967; 245320</t>
+          <t>172036; 242475</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>379017; 461354</t>
+          <t>381713; 466311</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>501766; 591069</t>
+          <t>502430; 595514</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>352827; 432517</t>
+          <t>351252; 430988</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>357869; 460265</t>
+          <t>358589; 466272</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P15-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P15-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,74%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,2; 6,98</t>
+          <t>4,11; 6,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,36; 9,84</t>
+          <t>6,27; 10,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,34; 7,73</t>
+          <t>4,67; 7,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,24; 9,37</t>
+          <t>4,89; 8,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,92; 7,52</t>
+          <t>4,68; 7,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,07; 10,09</t>
+          <t>7,06; 9,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,89; 9,52</t>
+          <t>5,87; 9,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,09; 12,15</t>
+          <t>8,88; 12,24</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,92; 6,87</t>
+          <t>4,84; 6,87</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,14; 9,46</t>
+          <t>7,1; 9,36</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,69; 8,22</t>
+          <t>5,63; 8,16</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,01; 10,41</t>
+          <t>7,58; 9,92</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,71%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,21; 10,0</t>
+          <t>7,29; 10,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,04; 10,78</t>
+          <t>8,25; 10,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,9; 6,94</t>
+          <t>4,92; 6,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,91; 7,07</t>
+          <t>5,28; 7,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,53; 5,73</t>
+          <t>3,68; 5,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,5; 7,94</t>
+          <t>5,47; 7,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,47; 5,3</t>
+          <t>3,44; 5,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,33; 5,64</t>
+          <t>4,31; 6,22</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,86; 7,63</t>
+          <t>5,86; 7,62</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,1; 9,03</t>
+          <t>7,2; 8,95</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,46; 5,82</t>
+          <t>4,42; 5,84</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,97; 6,08</t>
+          <t>5,0; 6,48</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,33; 10,17</t>
+          <t>5,42; 9,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,66; 8,09</t>
+          <t>3,66; 7,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,74; 7,85</t>
+          <t>3,95; 7,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,48; 7,62</t>
+          <t>4,11; 8,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,2; 6,97</t>
+          <t>3,3; 7,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,15; 9,25</t>
+          <t>3,93; 8,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,75; 8,04</t>
+          <t>3,83; 8,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,58; 6,15</t>
+          <t>3,5; 6,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,86; 7,9</t>
+          <t>4,96; 7,98</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,43; 7,71</t>
+          <t>4,38; 7,76</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,27; 7,21</t>
+          <t>4,22; 7,18</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,84; 6,6</t>
+          <t>4,19; 6,8</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,48; 8,4</t>
+          <t>6,57; 8,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,53; 9,41</t>
+          <t>7,46; 9,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,08; 6,69</t>
+          <t>5,13; 6,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,48; 6,77</t>
+          <t>5,35; 7,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,5; 6,05</t>
+          <t>4,49; 6,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,41; 8,25</t>
+          <t>6,35; 8,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,62; 6,26</t>
+          <t>4,67; 6,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,71; 6,64</t>
+          <t>5,49; 6,92</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,74; 7,01</t>
+          <t>5,66; 6,94</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,2; 8,54</t>
+          <t>7,21; 8,49</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,08; 6,24</t>
+          <t>5,07; 6,23</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,05; 6,56</t>
+          <t>5,69; 6,86</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35606</t>
+          <t>37843</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>79554</t>
+          <t>84521</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>115160</t>
+          <t>122364</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>43361; 71979</t>
+          <t>42431; 70735</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>61939; 95860</t>
+          <t>61078; 97467</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32769; 58300</t>
+          <t>35248; 59008</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26981; 48251</t>
+          <t>28305; 49213</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>64713; 98925</t>
+          <t>61590; 98660</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>94564; 135045</t>
+          <t>94478; 132563</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>58576; 94646</t>
+          <t>58393; 95206</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>68711; 91824</t>
+          <t>73024; 100620</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>115552; 161307</t>
+          <t>113670; 161200</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>165127; 218708</t>
+          <t>164255; 216531</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>99503; 143804</t>
+          <t>98507; 142802</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>101759; 132273</t>
+          <t>106146; 138909</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>130042</t>
+          <t>140218</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>101957</t>
+          <t>111027</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>231999</t>
+          <t>251245</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>122076; 169265</t>
+          <t>123470; 170235</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>157846; 211690</t>
+          <t>162096; 210092</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>101819; 144095</t>
+          <t>102243; 142726</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>89655; 161968</t>
+          <t>117711; 170901</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>56050; 90909</t>
+          <t>58432; 91216</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>96659; 139530</t>
+          <t>96184; 136388</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>69051; 105455</t>
+          <t>68347; 105413</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>74458; 126286</t>
+          <t>93502; 135064</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>192117; 250188</t>
+          <t>192324; 250070</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>264125; 336039</t>
+          <t>267879; 333060</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>181209; 236608</t>
+          <t>179468; 237422</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>179662; 275357</t>
+          <t>219912; 285099</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33226</t>
+          <t>41669</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>30866</t>
+          <t>35239</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>64092</t>
+          <t>76908</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>29402; 56100</t>
+          <t>29876; 54940</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>17620; 38947</t>
+          <t>17596; 37490</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20442; 42922</t>
+          <t>21600; 43464</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22520; 49295</t>
+          <t>29238; 61608</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>15237; 33224</t>
+          <t>15723; 34803</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19044; 42412</t>
+          <t>18028; 40957</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20618; 44127</t>
+          <t>21047; 44236</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>23612; 40625</t>
+          <t>25721; 45134</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>49962; 81194</t>
+          <t>51019; 82053</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>41647; 72458</t>
+          <t>41179; 72960</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>46850; 79024</t>
+          <t>46228; 78747</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>50233; 86321</t>
+          <t>60605; 98328</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>198874</t>
+          <t>219729</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>212377</t>
+          <t>230788</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>411252</t>
+          <t>450517</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>212290; 275280</t>
+          <t>215378; 275818</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>257533; 321909</t>
+          <t>255281; 321982</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>171679; 225857</t>
+          <t>173136; 228107</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>154496; 233781</t>
+          <t>188290; 252663</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>151993; 204526</t>
+          <t>151737; 203313</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>227761; 293375</t>
+          <t>225783; 287235</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>163040; 221032</t>
+          <t>165114; 223138</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>172036; 242475</t>
+          <t>204535; 258138</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>381713; 466311</t>
+          <t>376930; 462125</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>502430; 595514</t>
+          <t>502918; 592317</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>351252; 430988</t>
+          <t>350062; 430630</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>358589; 466272</t>
+          <t>412263; 497354</t>
         </is>
       </c>
     </row>
